--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_终局（上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="548">
   <si>
     <t>ID</t>
   </si>
@@ -768,6 +768,9 @@
     <t>屏幕暗下去之前，索菲亚的声音从你身后传来，细得几乎被散热风扇的嗡鸣盖过。她没有看着屏幕，她看着地面，指尖按在桌沿，指节发白。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <t>parallel(memoryoff();bgfade(sntzm_final(1)_73,1))</t>
   </si>
   <si>
@@ -784,6 +787,9 @@
   </si>
   <si>
     <t>这是真的......</t>
+  </si>
+  <si>
+    <t>7 enhanced litesaturation-horror</t>
   </si>
   <si>
     <t>源类型=type:txt_Sophia; 层级=73</t>
@@ -1150,6 +1156,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -5306,7 +5317,7 @@
         <v>212</v>
       </c>
       <c r="B64" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
@@ -5344,7 +5355,7 @@
         <v>215</v>
       </c>
       <c r="B65" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -5382,7 +5393,7 @@
         <v>218</v>
       </c>
       <c r="B66" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -5707,30 +5718,30 @@
         <v>15</v>
       </c>
       <c r="I74" t="s">
-        <v>15</v>
+        <v>244</v>
       </c>
       <c r="J74" t="s">
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L74" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="75" ht="30" spans="1:12">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="75" ht="45" spans="1:12">
       <c r="A75" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B75" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -5739,13 +5750,13 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
       </c>
       <c r="I75" t="s">
-        <v>15</v>
+        <v>251</v>
       </c>
       <c r="J75" t="s">
         <v>15</v>
@@ -5754,21 +5765,21 @@
         <v>58</v>
       </c>
       <c r="L75" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="76" ht="40.5" spans="1:12">
       <c r="A76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B76" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E76" t="s">
         <v>15</v>
@@ -5777,7 +5788,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5792,12 +5803,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="77" ht="55.5" spans="1:12">
       <c r="A77" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5806,7 +5817,7 @@
         <v>14</v>
       </c>
       <c r="D77" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E77" t="s">
         <v>15</v>
@@ -5815,7 +5826,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5830,12 +5841,12 @@
         <v>68</v>
       </c>
       <c r="L77" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B78" t="s">
         <v>55</v>
@@ -5853,7 +5864,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5868,12 +5879,12 @@
         <v>58</v>
       </c>
       <c r="L78" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B79" t="s">
         <v>55</v>
@@ -5891,7 +5902,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5906,12 +5917,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="80" ht="40.5" spans="1:12">
       <c r="A80" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5929,7 +5940,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5944,21 +5955,21 @@
         <v>68</v>
       </c>
       <c r="L80" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="81" ht="30" spans="1:12">
       <c r="A81" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B81" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
       </c>
       <c r="D81" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E81" t="s">
         <v>15</v>
@@ -5967,7 +5978,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5982,12 +5993,12 @@
         <v>58</v>
       </c>
       <c r="L81" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="82" ht="30" spans="1:12">
       <c r="A82" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5996,7 +6007,7 @@
         <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E82" t="s">
         <v>15</v>
@@ -6005,7 +6016,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -6020,12 +6031,12 @@
         <v>68</v>
       </c>
       <c r="L82" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="83" ht="69" spans="1:12">
       <c r="A83" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -6043,7 +6054,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -6058,12 +6069,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B84" t="s">
         <v>55</v>
@@ -6081,7 +6092,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6096,12 +6107,12 @@
         <v>58</v>
       </c>
       <c r="L84" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="85" ht="69" spans="1:12">
       <c r="A85" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6119,7 +6130,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6131,15 +6142,15 @@
         <v>15</v>
       </c>
       <c r="K85" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L85" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="86" ht="43.5" spans="1:12">
       <c r="A86" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6157,7 +6168,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6169,12 +6180,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B87" t="s">
         <v>55</v>
@@ -6192,7 +6203,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6207,12 +6218,12 @@
         <v>58</v>
       </c>
       <c r="L87" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="88" ht="57" spans="1:12">
       <c r="A88" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6230,7 +6241,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6245,12 +6256,12 @@
         <v>68</v>
       </c>
       <c r="L88" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="89" ht="27" spans="1:12">
       <c r="A89" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6268,7 +6279,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6283,12 +6294,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="90" ht="75" spans="1:12">
       <c r="A90" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6306,7 +6317,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6318,15 +6329,15 @@
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L90" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="91" ht="57" spans="1:12">
       <c r="A91" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6344,7 +6355,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6359,12 +6370,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="92" ht="27" spans="1:12">
       <c r="A92" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6382,7 +6393,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6397,12 +6408,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="93" ht="42" spans="1:12">
       <c r="A93" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6420,7 +6431,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6435,12 +6446,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="94" ht="28.5" spans="1:12">
       <c r="A94" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6458,7 +6469,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6473,12 +6484,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="95" ht="75" spans="1:12">
       <c r="A95" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6496,7 +6507,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6511,12 +6522,12 @@
         <v>15</v>
       </c>
       <c r="L95" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="96" ht="55.5" spans="1:12">
       <c r="A96" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6534,7 +6545,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6549,12 +6560,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6572,7 +6583,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6587,12 +6598,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="98" ht="75" spans="1:12">
       <c r="A98" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6610,7 +6621,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6625,12 +6636,12 @@
         <v>15</v>
       </c>
       <c r="L98" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="99" ht="70.5" spans="1:12">
       <c r="A99" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6648,7 +6659,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6663,15 +6674,15 @@
         <v>15</v>
       </c>
       <c r="L99" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B100" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
@@ -6686,7 +6697,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6701,12 +6712,12 @@
         <v>15</v>
       </c>
       <c r="L100" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="101" ht="40.5" spans="1:12">
       <c r="A101" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -6724,7 +6735,7 @@
         <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="H101" t="s">
         <v>15</v>
@@ -6739,21 +6750,21 @@
         <v>15</v>
       </c>
       <c r="L101" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="102" ht="30" spans="1:12">
       <c r="A102" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B102" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C102" t="s">
         <v>14</v>
       </c>
       <c r="D102" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E102" t="s">
         <v>15</v>
@@ -6762,7 +6773,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H102" t="s">
         <v>15</v>
@@ -6777,21 +6788,21 @@
         <v>58</v>
       </c>
       <c r="L102" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="103" ht="57" spans="1:12">
       <c r="A103" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B103" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E103" t="s">
         <v>15</v>
@@ -6800,7 +6811,7 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H103" t="s">
         <v>15</v>
@@ -6815,12 +6826,12 @@
         <v>15</v>
       </c>
       <c r="L103" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="104" ht="40.5" spans="1:12">
       <c r="A104" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -6829,7 +6840,7 @@
         <v>14</v>
       </c>
       <c r="D104" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E104" t="s">
         <v>15</v>
@@ -6838,7 +6849,7 @@
         <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H104" t="s">
         <v>15</v>
@@ -6853,12 +6864,12 @@
         <v>68</v>
       </c>
       <c r="L104" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="105" ht="42" spans="1:12">
       <c r="A105" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
@@ -6876,7 +6887,7 @@
         <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H105" t="s">
         <v>15</v>
@@ -6891,12 +6902,12 @@
         <v>15</v>
       </c>
       <c r="L105" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="106" ht="27" spans="1:12">
       <c r="A106" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B106" t="s">
         <v>55</v>
@@ -6914,7 +6925,7 @@
         <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="H106" t="s">
         <v>15</v>
@@ -6929,12 +6940,12 @@
         <v>58</v>
       </c>
       <c r="L106" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="107" ht="42" spans="1:12">
       <c r="A107" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
@@ -6952,7 +6963,7 @@
         <v>15</v>
       </c>
       <c r="G107" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="H107" t="s">
         <v>15</v>
@@ -6967,21 +6978,21 @@
         <v>68</v>
       </c>
       <c r="L107" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="108" ht="55.5" spans="1:12">
       <c r="A108" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B108" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
       </c>
       <c r="D108" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E108" t="s">
         <v>15</v>
@@ -6990,7 +7001,7 @@
         <v>15</v>
       </c>
       <c r="G108" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H108" t="s">
         <v>15</v>
@@ -7005,12 +7016,12 @@
         <v>58</v>
       </c>
       <c r="L108" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="109" ht="54" spans="1:12">
       <c r="A109" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
@@ -7019,7 +7030,7 @@
         <v>14</v>
       </c>
       <c r="D109" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E109" t="s">
         <v>15</v>
@@ -7028,7 +7039,7 @@
         <v>15</v>
       </c>
       <c r="G109" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H109" t="s">
         <v>15</v>
@@ -7043,12 +7054,12 @@
         <v>68</v>
       </c>
       <c r="L109" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="110" ht="69" spans="1:12">
       <c r="A110" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
@@ -7066,7 +7077,7 @@
         <v>15</v>
       </c>
       <c r="G110" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="H110" t="s">
         <v>15</v>
@@ -7081,12 +7092,12 @@
         <v>15</v>
       </c>
       <c r="L110" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" ht="42" spans="1:12">
       <c r="A111" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
@@ -7104,7 +7115,7 @@
         <v>15</v>
       </c>
       <c r="G111" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H111" t="s">
         <v>15</v>
@@ -7119,12 +7130,12 @@
         <v>15</v>
       </c>
       <c r="L111" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="112" ht="55.5" spans="1:12">
       <c r="A112" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
@@ -7142,7 +7153,7 @@
         <v>15</v>
       </c>
       <c r="G112" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="H112" t="s">
         <v>15</v>
@@ -7157,12 +7168,12 @@
         <v>15</v>
       </c>
       <c r="L112" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" ht="27" spans="1:12">
       <c r="A113" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
@@ -7180,7 +7191,7 @@
         <v>15</v>
       </c>
       <c r="G113" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="H113" t="s">
         <v>15</v>
@@ -7192,10 +7203,10 @@
         <v>15</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L113" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>
@@ -7216,47 +7227,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B5" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -7264,7 +7275,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7272,7 +7283,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
@@ -7280,7 +7291,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B9" t="s">
         <v>88</v>
@@ -7288,50 +7299,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B10" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B13" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B14" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B15" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -7353,616 +7364,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B4" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B5" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C5" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D5" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E5" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B7" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B8" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C8" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B9" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B10" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B11" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C11" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E11" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B12" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C12" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="D12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F12" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B13" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C13" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E13" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F13" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B14" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="D14" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E14" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F14" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B15" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C15" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D15" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E15" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="F15" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B16" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C16" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D16" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E16" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F16" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B17" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C17" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="D17" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E17" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B18" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C18" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D18" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E18" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="F18" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B19" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C19" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D19" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E19" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F19" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B20" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C20" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="D20" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E20" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F20" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B21" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C21" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D21" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E21" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="F21" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B22" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C22" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D22" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E22" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F22" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B23" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C23" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D23" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E23" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F23" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B24" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C24" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D24" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E24" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="F24" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B25" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C25" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D25" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E25" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="F25" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B26" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C26" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D26" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="E26" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="F26" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B27" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C27" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D27" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E27" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="F27" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B28" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C28" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D28" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E28" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F28" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B29" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C29" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D29" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="E29" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="F29" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B30" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C30" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D30" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="E30" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F30" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B31" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D31" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_终局（上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="550">
   <si>
     <t>ID</t>
   </si>
@@ -96,7 +96,38 @@
     <t>项目代号：圣徒计划（Project Sanctus）</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=1; wherelist={"wheretype":"2","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"相信亚波伦","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]},{"sortnum":"2","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"端详飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1</t>
+    </r>
   </si>
   <si>
     <t>4</t>
@@ -792,6 +823,9 @@
     <t>7 enhanced litesaturation-horror</t>
   </si>
   <si>
+    <t>charfadein(L,1)&amp;unlockmusic(Music7)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Sophia; 层级=73</t>
   </si>
   <si>
@@ -808,6 +842,9 @@
   </si>
   <si>
     <t>如果这里的试验体都是为了被做成芯片，成为武器而诞生的话，那么这里也就不再是什么精神病院，而是一个被机械设备、试验体以及层层谎言所包裹的“生物兵工厂”。</t>
+  </si>
+  <si>
+    <t>charfadeout(L,1)&amp;unlockscene(scene6)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=75</t>
@@ -1761,6 +1798,11 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1913,11 +1955,6 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -2226,31 +2263,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2259,124 +2293,130 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3003,7 +3043,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" ht="150" spans="1:12">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -3037,7 +3077,7 @@
       <c r="K3" t="s">
         <v>15</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5762,15 +5802,15 @@
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>58</v>
+        <v>252</v>
       </c>
       <c r="L75" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="76" ht="40.5" spans="1:12">
       <c r="A76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B76" t="s">
         <v>248</v>
@@ -5788,7 +5828,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5803,12 +5843,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77" ht="55.5" spans="1:12">
       <c r="A77" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5826,7 +5866,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5838,15 +5878,15 @@
         <v>15</v>
       </c>
       <c r="K77" t="s">
-        <v>68</v>
+        <v>259</v>
       </c>
       <c r="L77" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B78" t="s">
         <v>55</v>
@@ -5864,7 +5904,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5879,12 +5919,12 @@
         <v>58</v>
       </c>
       <c r="L78" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B79" t="s">
         <v>55</v>
@@ -5902,7 +5942,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5917,12 +5957,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" ht="40.5" spans="1:12">
       <c r="A80" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5940,7 +5980,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5955,12 +5995,12 @@
         <v>68</v>
       </c>
       <c r="L80" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="81" ht="30" spans="1:12">
       <c r="A81" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B81" t="s">
         <v>248</v>
@@ -5978,7 +6018,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5993,12 +6033,12 @@
         <v>58</v>
       </c>
       <c r="L81" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="82" ht="30" spans="1:12">
       <c r="A82" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -6016,7 +6056,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -6031,12 +6071,12 @@
         <v>68</v>
       </c>
       <c r="L82" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83" ht="69" spans="1:12">
       <c r="A83" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B83" t="s">
         <v>13</v>
@@ -6054,7 +6094,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -6069,12 +6109,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B84" t="s">
         <v>55</v>
@@ -6092,7 +6132,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6107,12 +6147,12 @@
         <v>58</v>
       </c>
       <c r="L84" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="85" ht="69" spans="1:12">
       <c r="A85" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B85" t="s">
         <v>13</v>
@@ -6130,7 +6170,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6142,15 +6182,15 @@
         <v>15</v>
       </c>
       <c r="K85" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L85" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" ht="43.5" spans="1:12">
       <c r="A86" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6168,7 +6208,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6180,12 +6220,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B87" t="s">
         <v>55</v>
@@ -6203,7 +6243,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6218,12 +6258,12 @@
         <v>58</v>
       </c>
       <c r="L87" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="88" ht="57" spans="1:12">
       <c r="A88" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B88" t="s">
         <v>13</v>
@@ -6241,7 +6281,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6256,12 +6296,12 @@
         <v>68</v>
       </c>
       <c r="L88" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="89" ht="27" spans="1:12">
       <c r="A89" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6279,7 +6319,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6294,12 +6334,12 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="90" ht="75" spans="1:12">
       <c r="A90" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B90" t="s">
         <v>13</v>
@@ -6317,7 +6357,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6329,15 +6369,15 @@
         <v>15</v>
       </c>
       <c r="K90" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="L90" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="91" ht="57" spans="1:12">
       <c r="A91" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6355,7 +6395,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6370,12 +6410,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="92" ht="27" spans="1:12">
       <c r="A92" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6393,7 +6433,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6408,12 +6448,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="93" ht="42" spans="1:12">
       <c r="A93" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6431,7 +6471,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6446,12 +6486,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="94" ht="28.5" spans="1:12">
       <c r="A94" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6469,7 +6509,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6484,12 +6524,12 @@
         <v>15</v>
       </c>
       <c r="L94" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="95" ht="75" spans="1:12">
       <c r="A95" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6507,7 +6547,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6522,12 +6562,12 @@
         <v>15</v>
       </c>
       <c r="L95" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="96" ht="55.5" spans="1:12">
       <c r="A96" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6545,7 +6585,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6560,12 +6600,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B97" t="s">
         <v>13</v>
@@ -6583,7 +6623,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6598,12 +6638,12 @@
         <v>15</v>
       </c>
       <c r="L97" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="98" ht="75" spans="1:12">
       <c r="A98" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6621,7 +6661,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6636,12 +6676,12 @@
         <v>15</v>
       </c>
       <c r="L98" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="99" ht="70.5" spans="1:12">
       <c r="A99" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6659,7 +6699,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6674,15 +6714,15 @@
         <v>15</v>
       </c>
       <c r="L99" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B100" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
@@ -6697,7 +6737,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6712,12 +6752,12 @@
         <v>15</v>
       </c>
       <c r="L100" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="101" ht="40.5" spans="1:12">
       <c r="A101" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -6735,7 +6775,7 @@
         <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H101" t="s">
         <v>15</v>
@@ -6750,12 +6790,12 @@
         <v>15</v>
       </c>
       <c r="L101" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="102" ht="30" spans="1:12">
       <c r="A102" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B102" t="s">
         <v>248</v>
@@ -6773,7 +6813,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H102" t="s">
         <v>15</v>
@@ -6788,12 +6828,12 @@
         <v>58</v>
       </c>
       <c r="L102" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="103" ht="57" spans="1:12">
       <c r="A103" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B103" t="s">
         <v>248</v>
@@ -6811,7 +6851,7 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="H103" t="s">
         <v>15</v>
@@ -6826,12 +6866,12 @@
         <v>15</v>
       </c>
       <c r="L103" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="104" ht="40.5" spans="1:12">
       <c r="A104" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B104" t="s">
         <v>13</v>
@@ -6849,7 +6889,7 @@
         <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="H104" t="s">
         <v>15</v>
@@ -6864,12 +6904,12 @@
         <v>68</v>
       </c>
       <c r="L104" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="105" ht="42" spans="1:12">
       <c r="A105" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
@@ -6887,7 +6927,7 @@
         <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H105" t="s">
         <v>15</v>
@@ -6902,12 +6942,12 @@
         <v>15</v>
       </c>
       <c r="L105" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="106" ht="27" spans="1:12">
       <c r="A106" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B106" t="s">
         <v>55</v>
@@ -6925,7 +6965,7 @@
         <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="H106" t="s">
         <v>15</v>
@@ -6940,12 +6980,12 @@
         <v>58</v>
       </c>
       <c r="L106" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="107" ht="42" spans="1:12">
       <c r="A107" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
@@ -6963,7 +7003,7 @@
         <v>15</v>
       </c>
       <c r="G107" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H107" t="s">
         <v>15</v>
@@ -6978,12 +7018,12 @@
         <v>68</v>
       </c>
       <c r="L107" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="108" ht="55.5" spans="1:12">
       <c r="A108" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B108" t="s">
         <v>248</v>
@@ -7001,7 +7041,7 @@
         <v>15</v>
       </c>
       <c r="G108" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H108" t="s">
         <v>15</v>
@@ -7016,12 +7056,12 @@
         <v>58</v>
       </c>
       <c r="L108" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="109" ht="54" spans="1:12">
       <c r="A109" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B109" t="s">
         <v>13</v>
@@ -7039,7 +7079,7 @@
         <v>15</v>
       </c>
       <c r="G109" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="H109" t="s">
         <v>15</v>
@@ -7054,12 +7094,12 @@
         <v>68</v>
       </c>
       <c r="L109" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" ht="69" spans="1:12">
       <c r="A110" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B110" t="s">
         <v>13</v>
@@ -7077,7 +7117,7 @@
         <v>15</v>
       </c>
       <c r="G110" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="H110" t="s">
         <v>15</v>
@@ -7092,12 +7132,12 @@
         <v>15</v>
       </c>
       <c r="L110" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="111" ht="42" spans="1:12">
       <c r="A111" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B111" t="s">
         <v>13</v>
@@ -7115,7 +7155,7 @@
         <v>15</v>
       </c>
       <c r="G111" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="H111" t="s">
         <v>15</v>
@@ -7130,12 +7170,12 @@
         <v>15</v>
       </c>
       <c r="L111" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" ht="55.5" spans="1:12">
       <c r="A112" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B112" t="s">
         <v>13</v>
@@ -7153,7 +7193,7 @@
         <v>15</v>
       </c>
       <c r="G112" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H112" t="s">
         <v>15</v>
@@ -7168,12 +7208,12 @@
         <v>15</v>
       </c>
       <c r="L112" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="113" ht="27" spans="1:12">
       <c r="A113" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B113" t="s">
         <v>13</v>
@@ -7191,7 +7231,7 @@
         <v>15</v>
       </c>
       <c r="G113" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="H113" t="s">
         <v>15</v>
@@ -7202,11 +7242,11 @@
       <c r="J113" t="s">
         <v>15</v>
       </c>
-      <c r="K113" s="2" t="s">
-        <v>369</v>
+      <c r="K113" s="3" t="s">
+        <v>371</v>
       </c>
       <c r="L113" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -7227,47 +7267,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B5" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -7275,7 +7315,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7283,7 +7323,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B8" t="s">
         <v>109</v>
@@ -7291,7 +7331,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B9" t="s">
         <v>88</v>
@@ -7299,50 +7339,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B10" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B11" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B12" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B14" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B15" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -7364,616 +7404,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B4" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="D4" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="F4" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B5" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C5" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D5" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F5" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B7" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D7" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F7" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B8" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C8" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D8" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E8" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="F8" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B9" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F9" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B10" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C10" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D10" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E10" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F10" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B11" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C11" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D11" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E11" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F11" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B12" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="D12" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E12" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F12" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B13" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C13" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D13" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E13" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F13" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B14" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C14" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D14" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E14" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F14" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B15" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C15" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D15" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E15" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F15" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B16" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C16" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D16" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E16" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F16" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B17" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C17" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D17" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E17" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="F17" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B18" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C18" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D18" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E18" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="F18" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B19" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C19" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D19" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E19" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F19" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B20" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C20" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D20" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E20" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F20" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B21" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C21" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D21" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E21" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="F21" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B22" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C22" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D22" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E22" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F22" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B23" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C23" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D23" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E23" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F23" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B24" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C24" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D24" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E24" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F24" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B25" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C25" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D25" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E25" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F25" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B26" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C26" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D26" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="E26" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="F26" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B27" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C27" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D27" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E27" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="F27" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B28" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C28" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D28" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="E28" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="F28" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B29" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C29" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="D29" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="E29" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F29" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B30" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C30" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D30" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="E30" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F30" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B31" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="C31" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D31" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
   </sheetData>
